--- a/result_efficiency.xlsx
+++ b/result_efficiency.xlsx
@@ -28,7 +28,24 @@
     <t xml:space="preserve">FLOAT</t>
   </si>
   <si>
-    <t xml:space="preserve">Производительность</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Производительность, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">млн. отсчетов/сек  ///  № замера</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Длина окна</t>
@@ -46,9 +63,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00E+00"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -67,6 +84,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
     </font>
@@ -364,25 +387,25 @@
             <c:numRef>
               <c:f>Лист1!$B$14:$B$19</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8957800000</c:v>
+                  <c:v>9327.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8299000000</c:v>
+                  <c:v>12934.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3935800000</c:v>
+                  <c:v>6856.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1128400000</c:v>
+                  <c:v>2454.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>495000000</c:v>
+                  <c:v>1418.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>245000000</c:v>
+                  <c:v>575.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -483,25 +506,25 @@
             <c:numRef>
               <c:f>Лист1!$B$4:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>19078600000</c:v>
+                  <c:v>8175</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11666600000</c:v>
+                  <c:v>12635.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7478200000</c:v>
+                  <c:v>7412</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2954800000</c:v>
+                  <c:v>2866.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1089400000</c:v>
+                  <c:v>1464.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>486400000</c:v>
+                  <c:v>692.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -516,11 +539,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="33076751"/>
-        <c:axId val="41244630"/>
+        <c:axId val="63375674"/>
+        <c:axId val="88004192"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33076751"/>
+        <c:axId val="63375674"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -588,7 +611,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41244630"/>
+        <c:crossAx val="88004192"/>
         <c:crossesAt val="1"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -596,7 +619,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41244630"/>
+        <c:axId val="88004192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -635,7 +658,7 @@
                     <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Усредненная производительность, 
-отсчетов/сек</a:t>
+млн. отсчетов/сек</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -648,7 +671,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -674,8 +697,8 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33076751"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="63375674"/>
+        <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -730,16 +753,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>613800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>475200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>88200</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>762120</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -747,8 +770,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7116120" y="754920"/>
-        <a:ext cx="7602480" cy="3948840"/>
+        <a:off x="6164640" y="248040"/>
+        <a:ext cx="7602120" cy="3948480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -922,22 +945,22 @@
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">AVERAGE(C4:G4)</f>
-        <v>19078600000</v>
+        <v>8175</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>23809000000</v>
+        <v>9615</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7299000000</v>
+        <v>12820</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>28571000000</v>
+        <v>4405</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>17857000000</v>
+        <v>3831</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>17857000000</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -946,22 +969,22 @@
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">AVERAGE(C5:G5)</f>
-        <v>11666600000</v>
+        <v>12635.2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>12345000000</v>
+        <v>9174</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>11111000000</v>
+        <v>13333</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>10000000000</v>
+        <v>8130</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10989000000</v>
+        <v>15873</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>13888000000</v>
+        <v>16666</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -970,22 +993,22 @@
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">AVERAGE(C6:G6)</f>
-        <v>7478200000</v>
+        <v>7412</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11904000000</v>
+        <v>6024</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9090000000</v>
+        <v>6578</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1851000000</v>
+        <v>8064</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7194000000</v>
+        <v>8264</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7352000000</v>
+        <v>8130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -994,22 +1017,22 @@
       </c>
       <c r="B7" s="4" t="n">
         <f aca="false">AVERAGE(C7:G7)</f>
-        <v>2954800000</v>
+        <v>2866.4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4291000000</v>
+        <v>2469</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3125000000</v>
+        <v>3236</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1623000000</v>
+        <v>1795</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3125000000</v>
+        <v>3521</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2610000000</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1018,22 +1041,22 @@
       </c>
       <c r="B8" s="4" t="n">
         <f aca="false">AVERAGE(C8:G8)</f>
-        <v>1089400000</v>
+        <v>1464.8</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1557000000</v>
+        <v>1366</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>396000000</v>
+        <v>1430</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1132000000</v>
+        <v>992</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>840000000</v>
+        <v>1818</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1522000000</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1042,22 +1065,22 @@
       </c>
       <c r="B9" s="4" t="n">
         <f aca="false">AVERAGE(C9:G9)</f>
-        <v>486400000</v>
+        <v>692.8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>999000000</v>
+        <v>691</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>83000000</v>
+        <v>735</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>592000000</v>
+        <v>484</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>336000000</v>
+        <v>789</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>422000000</v>
+        <v>765</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1107,22 +1130,22 @@
       </c>
       <c r="B14" s="4" t="n">
         <f aca="false">AVERAGE(C14:G14)</f>
-        <v>8957800000</v>
+        <v>9327.2</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7692000000</v>
+        <v>11494</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>14084000000</v>
+        <v>11904</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2710000000</v>
+        <v>9433</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18518000000</v>
+        <v>10309</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1785000000</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1131,22 +1154,22 @@
       </c>
       <c r="B15" s="4" t="n">
         <f aca="false">AVERAGE(C15:G15)</f>
-        <v>8299000000</v>
+        <v>12934.8</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>13333000000</v>
+        <v>16129</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>9900000000</v>
+        <v>11627</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2873000000</v>
+        <v>12820</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>14084000000</v>
+        <v>12987</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1305000000</v>
+        <v>11111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1155,22 +1178,22 @@
       </c>
       <c r="B16" s="4" t="n">
         <f aca="false">AVERAGE(C16:G16)</f>
-        <v>3935800000</v>
+        <v>6856.2</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>6944000000</v>
+        <v>6756</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5263000000</v>
+        <v>6097</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2638000000</v>
+        <v>7518</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4347000000</v>
+        <v>8196</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>487000000</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1179,22 +1202,22 @@
       </c>
       <c r="B17" s="4" t="n">
         <f aca="false">AVERAGE(C17:G17)</f>
-        <v>1128400000</v>
+        <v>2454.8</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2283000000</v>
+        <v>3759</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1515000000</v>
+        <v>2237</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1293000000</v>
+        <v>1485</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>275000000</v>
+        <v>2169</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>276000000</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1203,22 +1226,22 @@
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">AVERAGE(C18:G18)</f>
-        <v>495000000</v>
+        <v>1418.8</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>343000000</v>
+        <v>2610</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>810000000</v>
+        <v>1069</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1061000000</v>
+        <v>1336</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>131000000</v>
+        <v>1243</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>130000000</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1227,22 +1250,22 @@
       </c>
       <c r="B19" s="4" t="n">
         <f aca="false">AVERAGE(C19:G19)</f>
-        <v>245000000</v>
+        <v>575.2</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>299000000</v>
+        <v>784</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>385000000</v>
+        <v>574</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>407000000</v>
+        <v>472</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>67000000</v>
+        <v>555</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>67000000</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
